--- a/BWI/bestwine_output/bestwine_Monaco.xlsx
+++ b/BWI/bestwine_output/bestwine_Monaco.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,8 +35,11 @@
     <font>
       <color rgb="00000000"/>
     </font>
+    <font>
+      <color rgb="00276221"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +56,11 @@
         <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -66,13 +74,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA25"/>
+  <dimension ref="A1:AA28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2767,6 +2776,297 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Latina S. A. M</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Latina S. A. M</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>62858</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>17 Boulevard Rainier</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>98000</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>https://latina.mc</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr"/>
+      <c r="L26" s="4" t="inlineStr"/>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>s.jaber@latina.mc</t>
+        </is>
+      </c>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>+377 97 77 83 04</t>
+        </is>
+      </c>
+      <c r="P26" s="4" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr"/>
+      <c r="R26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/latina-s-a-m/</t>
+        </is>
+      </c>
+      <c r="S26" s="4" t="inlineStr"/>
+      <c r="T26" s="4" t="inlineStr"/>
+      <c r="U26" s="4" t="inlineStr"/>
+      <c r="V26" s="4" t="inlineStr"/>
+      <c r="W26" s="4" t="inlineStr">
+        <is>
+          <t>Diana Shu</t>
+        </is>
+      </c>
+      <c r="X26" s="4" t="inlineStr">
+        <is>
+          <t>Sales And Purchase Manager</t>
+        </is>
+      </c>
+      <c r="Y26" s="4" t="inlineStr"/>
+      <c r="Z26" s="4" t="inlineStr"/>
+      <c r="AA26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/diana-shu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Latina S. A. M</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Latina S. A. M</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>62858</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>17 Boulevard Rainier</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>98000</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>https://latina.mc</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr"/>
+      <c r="L27" s="4" t="inlineStr"/>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>s.jaber@latina.mc</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>+377 97 77 83 04</t>
+        </is>
+      </c>
+      <c r="P27" s="4" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q27" s="4" t="inlineStr"/>
+      <c r="R27" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/latina-s-a-m/</t>
+        </is>
+      </c>
+      <c r="S27" s="4" t="inlineStr"/>
+      <c r="T27" s="4" t="inlineStr"/>
+      <c r="U27" s="4" t="inlineStr"/>
+      <c r="V27" s="4" t="inlineStr"/>
+      <c r="W27" s="4" t="inlineStr">
+        <is>
+          <t>Yanyang Zheng</t>
+        </is>
+      </c>
+      <c r="X27" s="4" t="inlineStr">
+        <is>
+          <t>Senior Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y27" s="4" t="inlineStr"/>
+      <c r="Z27" s="4" t="inlineStr"/>
+      <c r="AA27" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/yanyangzheng</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Latina S. A. M</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Latina S. A. M</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>62858</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>17 Boulevard Rainier</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>98000</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>https://latina.mc</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr"/>
+      <c r="L28" s="4" t="inlineStr"/>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>s.jaber@latina.mc</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>+377 97 77 83 04</t>
+        </is>
+      </c>
+      <c r="P28" s="4" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="inlineStr"/>
+      <c r="R28" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/latina-s-a-m/</t>
+        </is>
+      </c>
+      <c r="S28" s="4" t="inlineStr"/>
+      <c r="T28" s="4" t="inlineStr"/>
+      <c r="U28" s="4" t="inlineStr"/>
+      <c r="V28" s="4" t="inlineStr"/>
+      <c r="W28" s="4" t="inlineStr">
+        <is>
+          <t>Sami Jaber</t>
+        </is>
+      </c>
+      <c r="X28" s="4" t="inlineStr">
+        <is>
+          <t>Head of Purchase Department Wines, Spirits and Champagnes</t>
+        </is>
+      </c>
+      <c r="Y28" s="4" t="inlineStr"/>
+      <c r="Z28" s="4" t="inlineStr"/>
+      <c r="AA28" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sami-jaber-2b088415a/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Monaco.xlsx
+++ b/BWI/bestwine_output/bestwine_Monaco.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA28"/>
+  <dimension ref="A1:AA31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3067,6 +3067,297 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Latina S. A. M</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Latina S. A. M</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>62858</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>17 Boulevard Rainier</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>98000</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>https://latina.mc</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr"/>
+      <c r="L29" s="4" t="inlineStr"/>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>s.jaber@latina.mc</t>
+        </is>
+      </c>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>+377 97 77 83 04</t>
+        </is>
+      </c>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q29" s="4" t="inlineStr"/>
+      <c r="R29" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/latina-s-a-m/</t>
+        </is>
+      </c>
+      <c r="S29" s="4" t="inlineStr"/>
+      <c r="T29" s="4" t="inlineStr"/>
+      <c r="U29" s="4" t="inlineStr"/>
+      <c r="V29" s="4" t="inlineStr"/>
+      <c r="W29" s="4" t="inlineStr">
+        <is>
+          <t>Sami Jaber</t>
+        </is>
+      </c>
+      <c r="X29" s="4" t="inlineStr">
+        <is>
+          <t>Head of Purchase Department Wines, Spirits and Champagnes</t>
+        </is>
+      </c>
+      <c r="Y29" s="4" t="inlineStr"/>
+      <c r="Z29" s="4" t="inlineStr"/>
+      <c r="AA29" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sami-jaber-2b088415a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Latina S. A. M</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Latina S. A. M</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>62858</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>17 Boulevard Rainier</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>98000</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>https://latina.mc</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr"/>
+      <c r="L30" s="4" t="inlineStr"/>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>s.jaber@latina.mc</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>+377 97 77 83 04</t>
+        </is>
+      </c>
+      <c r="P30" s="4" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="inlineStr"/>
+      <c r="R30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/latina-s-a-m/</t>
+        </is>
+      </c>
+      <c r="S30" s="4" t="inlineStr"/>
+      <c r="T30" s="4" t="inlineStr"/>
+      <c r="U30" s="4" t="inlineStr"/>
+      <c r="V30" s="4" t="inlineStr"/>
+      <c r="W30" s="4" t="inlineStr">
+        <is>
+          <t>Diana Shu</t>
+        </is>
+      </c>
+      <c r="X30" s="4" t="inlineStr">
+        <is>
+          <t>Sales And Purchase Manager</t>
+        </is>
+      </c>
+      <c r="Y30" s="4" t="inlineStr"/>
+      <c r="Z30" s="4" t="inlineStr"/>
+      <c r="AA30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/diana-shu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Latina S. A. M</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Latina S. A. M</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>62858</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>17 Boulevard Rainier</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>98000</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>https://latina.mc</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr"/>
+      <c r="L31" s="4" t="inlineStr"/>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>s.jaber@latina.mc</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>+377 97 77 83 04</t>
+        </is>
+      </c>
+      <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="inlineStr"/>
+      <c r="R31" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/latina-s-a-m/</t>
+        </is>
+      </c>
+      <c r="S31" s="4" t="inlineStr"/>
+      <c r="T31" s="4" t="inlineStr"/>
+      <c r="U31" s="4" t="inlineStr"/>
+      <c r="V31" s="4" t="inlineStr"/>
+      <c r="W31" s="4" t="inlineStr">
+        <is>
+          <t>Yanyang Zheng</t>
+        </is>
+      </c>
+      <c r="X31" s="4" t="inlineStr">
+        <is>
+          <t>Senior Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y31" s="4" t="inlineStr"/>
+      <c r="Z31" s="4" t="inlineStr"/>
+      <c r="AA31" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/yanyangzheng</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
